--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>91360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R5" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>91358</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R6" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,14 +1153,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384266</v>
+        <v>128384263</v>
       </c>
       <c r="B7" t="n">
         <v>79032</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730098</v>
+        <v>730037</v>
       </c>
       <c r="R7" t="n">
-        <v>7119677</v>
+        <v>7119646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B8" t="n">
         <v>79032</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R8" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384263</v>
+        <v>128384251</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730037</v>
+        <v>730051</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384266</v>
+        <v>128384263</v>
       </c>
       <c r="B8" t="n">
         <v>79032</v>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730098</v>
+        <v>730037</v>
       </c>
       <c r="R8" t="n">
-        <v>7119677</v>
+        <v>7119646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384251</v>
+        <v>128384266</v>
       </c>
       <c r="B9" t="n">
-        <v>57673</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730051</v>
+        <v>730098</v>
       </c>
       <c r="R9" t="n">
-        <v>7119629</v>
+        <v>7119677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1425,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384251</v>
+        <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730051</v>
+        <v>730037</v>
       </c>
       <c r="R7" t="n">
-        <v>7119629</v>
+        <v>7119646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R8" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384266</v>
+        <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730098</v>
+        <v>730051</v>
       </c>
       <c r="R9" t="n">
-        <v>7119677</v>
+        <v>7119629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B5" t="n">
-        <v>91452</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R5" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>91464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R6" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128384266</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>91466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R5" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>91464</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R6" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128384266</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384263</v>
+        <v>128384251</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730037</v>
+        <v>730051</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384266</v>
+        <v>128384263</v>
       </c>
       <c r="B8" t="n">
         <v>79089</v>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730098</v>
+        <v>730037</v>
       </c>
       <c r="R8" t="n">
-        <v>7119677</v>
+        <v>7119646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384251</v>
+        <v>128384266</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730051</v>
+        <v>730098</v>
       </c>
       <c r="R9" t="n">
-        <v>7119629</v>
+        <v>7119677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1425,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B5" t="n">
-        <v>91466</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R5" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>91467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R6" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384251</v>
+        <v>128384266</v>
       </c>
       <c r="B7" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730051</v>
+        <v>730098</v>
       </c>
       <c r="R7" t="n">
-        <v>7119629</v>
+        <v>7119677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384266</v>
+        <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730098</v>
+        <v>730051</v>
       </c>
       <c r="R9" t="n">
-        <v>7119677</v>
+        <v>7119629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>91494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R5" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>91467</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R6" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384266</v>
+        <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730098</v>
+        <v>730037</v>
       </c>
       <c r="R7" t="n">
-        <v>7119677</v>
+        <v>7119646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R8" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384266</v>
+        <v>128384251</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730098</v>
+        <v>730051</v>
       </c>
       <c r="R8" t="n">
-        <v>7119677</v>
+        <v>7119629</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384251</v>
+        <v>128384266</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730051</v>
+        <v>730098</v>
       </c>
       <c r="R9" t="n">
-        <v>7119629</v>
+        <v>7119677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1425,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B5" t="n">
-        <v>91494</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R5" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R6" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384263</v>
+        <v>128384251</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730037</v>
+        <v>730051</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384251</v>
+        <v>128384263</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730051</v>
+        <v>730037</v>
       </c>
       <c r="R8" t="n">
-        <v>7119629</v>
+        <v>7119646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1328,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,7 +1362,7 @@
         <v>128384266</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384268</v>
+        <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730060</v>
+        <v>730066</v>
       </c>
       <c r="R5" t="n">
-        <v>7119639</v>
+        <v>7119649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384244</v>
+        <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730066</v>
+        <v>730060</v>
       </c>
       <c r="R6" t="n">
-        <v>7119649</v>
+        <v>7119639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384251</v>
+        <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730051</v>
+        <v>730037</v>
       </c>
       <c r="R7" t="n">
-        <v>7119629</v>
+        <v>7119646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B8" t="n">
         <v>79120</v>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R8" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384266</v>
+        <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730098</v>
+        <v>730051</v>
       </c>
       <c r="R9" t="n">
-        <v>7119677</v>
+        <v>7119629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384263</v>
+        <v>128384251</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730037</v>
+        <v>730051</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119629</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384266</v>
+        <v>128384263</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730098</v>
+        <v>730037</v>
       </c>
       <c r="R8" t="n">
-        <v>7119677</v>
+        <v>7119646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384251</v>
+        <v>128384266</v>
       </c>
       <c r="B9" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730051</v>
+        <v>730098</v>
       </c>
       <c r="R9" t="n">
-        <v>7119629</v>
+        <v>7119677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1425,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384251</v>
+        <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>79124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730051</v>
+        <v>730037</v>
       </c>
       <c r="R7" t="n">
-        <v>7119629</v>
+        <v>7119646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B8" t="n">
         <v>79124</v>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R8" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384266</v>
+        <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730098</v>
+        <v>730051</v>
       </c>
       <c r="R9" t="n">
-        <v>7119677</v>
+        <v>7119629</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128384267</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128384264</v>
       </c>
       <c r="B3" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128384244</v>
       </c>
       <c r="B5" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128384268</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128384263</v>
       </c>
       <c r="B7" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128384266</v>
       </c>
       <c r="B8" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128384251</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>128384261</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>128384276</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128384267</v>
+        <v>128384244</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730079</v>
+        <v>730066</v>
       </c>
       <c r="R2" t="n">
-        <v>7119653</v>
+        <v>7119649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,21 +765,21 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128384264</v>
+        <v>128384261</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730085</v>
+        <v>730038</v>
       </c>
       <c r="R3" t="n">
-        <v>7119704</v>
+        <v>7119597</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,11 +872,11 @@
         <v>128384262</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128384244</v>
+        <v>128384263</v>
       </c>
       <c r="B5" t="n">
-        <v>91513</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730066</v>
+        <v>730037</v>
       </c>
       <c r="R5" t="n">
-        <v>7119649</v>
+        <v>7119646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128384268</v>
+        <v>128384264</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730060</v>
+        <v>730085</v>
       </c>
       <c r="R6" t="n">
-        <v>7119639</v>
+        <v>7119704</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,21 +1153,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128384263</v>
+        <v>128384266</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730037</v>
+        <v>730098</v>
       </c>
       <c r="R7" t="n">
-        <v>7119646</v>
+        <v>7119677</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128384266</v>
+        <v>128384267</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730098</v>
+        <v>730079</v>
       </c>
       <c r="R8" t="n">
-        <v>7119677</v>
+        <v>7119653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,39 +1347,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128384251</v>
+        <v>128384268</v>
       </c>
       <c r="B9" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730051</v>
+        <v>730060</v>
       </c>
       <c r="R9" t="n">
-        <v>7119629</v>
+        <v>7119639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1427,11 +1427,6 @@
           <t>2025-09-10</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1449,21 +1444,21 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128384261</v>
+        <v>128384276</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730038</v>
+        <v>730074</v>
       </c>
       <c r="R10" t="n">
-        <v>7119597</v>
+        <v>7119707</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,17 +1541,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128384276</v>
+        <v>128384251</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730074</v>
+        <v>730051</v>
       </c>
       <c r="R11" t="n">
-        <v>7119707</v>
+        <v>7119629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1626,6 +1621,11 @@
           <t>2025-09-10</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 28708-2024 artfynd.xlsx
+++ b/artfynd/A 28708-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384261</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384262</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384263</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384264</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384266</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384267</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384268</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384276</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,8 +1697,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128384251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>